--- a/data/trans_dic/P2A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación</t>
+          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,95; 48,95</t>
+          <t>37,17; 49,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54,92; 66,72</t>
+          <t>55,68; 66,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50,66; 62,79</t>
+          <t>50,62; 62,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58,51; 70,89</t>
+          <t>57,97; 70,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,92; 58,5</t>
+          <t>45,42; 58,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,43; 83,39</t>
+          <t>73,36; 83,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,32; 73,86</t>
+          <t>63,62; 74,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>66,03; 74,62</t>
+          <t>66,17; 75,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42,85; 51,92</t>
+          <t>43,12; 51,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65,43; 73,35</t>
+          <t>65,61; 73,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58,94; 67,14</t>
+          <t>57,91; 66,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,57; 71,54</t>
+          <t>63,41; 71,17</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,19; 51,04</t>
+          <t>42,5; 51,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,15; 57,85</t>
+          <t>48,24; 57,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52,74; 62,08</t>
+          <t>52,59; 61,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35,26; 46,11</t>
+          <t>34,94; 45,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>61,31; 69,63</t>
+          <t>61,44; 69,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,78; 74,25</t>
+          <t>66,21; 74,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,88; 75,01</t>
+          <t>67,08; 74,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>42,1; 49,81</t>
+          <t>41,58; 49,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53,31; 59,34</t>
+          <t>53,18; 59,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58,47; 65,11</t>
+          <t>58,1; 64,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61,43; 67,46</t>
+          <t>61,15; 67,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,42; 46,22</t>
+          <t>39,58; 46,64</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,09; 50,19</t>
+          <t>39,49; 50,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53,04; 64,44</t>
+          <t>54,17; 65,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47,66; 57,83</t>
+          <t>47,62; 58,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43,02; 54,33</t>
+          <t>43,52; 54,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62,65; 73,1</t>
+          <t>63,12; 73,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,79; 73,32</t>
+          <t>63,3; 73,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,62; 66,39</t>
+          <t>56,69; 66,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,62; 55,86</t>
+          <t>46,55; 55,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52,68; 60,48</t>
+          <t>52,55; 60,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>60,35; 68,0</t>
+          <t>60,21; 67,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>53,65; 61,23</t>
+          <t>53,61; 61,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46,56; 53,6</t>
+          <t>45,99; 53,47</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,62; 57,67</t>
+          <t>46,68; 56,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,43; 64,12</t>
+          <t>53,84; 64,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53,52; 63,36</t>
+          <t>53,15; 63,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38,18; 51,93</t>
+          <t>37,59; 51,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>64,87; 74,67</t>
+          <t>64,66; 74,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,72; 75,7</t>
+          <t>66,32; 76,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,48; 75,78</t>
+          <t>66,02; 75,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,32; 51,27</t>
+          <t>24,69; 51,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>57,42; 64,47</t>
+          <t>57,25; 64,45</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61,55; 68,64</t>
+          <t>61,71; 68,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61,14; 68,21</t>
+          <t>61,35; 68,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,84; 49,01</t>
+          <t>30,79; 48,95</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,68; 56,49</t>
+          <t>42,82; 56,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49,52; 63,39</t>
+          <t>48,86; 63,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,67; 59,75</t>
+          <t>45,17; 59,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,52; 17,44</t>
+          <t>9,4; 17,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,66; 72,06</t>
+          <t>58,8; 72,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,07; 86,92</t>
+          <t>76,6; 87,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,88; 70,55</t>
+          <t>57,57; 70,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,89; 19,35</t>
+          <t>8,13; 19,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>52,6; 62,54</t>
+          <t>52,66; 62,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65,3; 73,91</t>
+          <t>64,86; 73,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53,93; 63,22</t>
+          <t>54,48; 63,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,54; 17,23</t>
+          <t>9,56; 17,14</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44,72; 56,76</t>
+          <t>44,87; 57,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>56,41; 68,86</t>
+          <t>56,1; 68,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43,44; 56,13</t>
+          <t>43,28; 55,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51,47; 62,72</t>
+          <t>51,92; 63,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58,3; 70,09</t>
+          <t>58,6; 70,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72,21; 82,15</t>
+          <t>72,38; 82,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55,68; 67,45</t>
+          <t>56,68; 68,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>52,39; 62,22</t>
+          <t>52,69; 62,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53,78; 62,24</t>
+          <t>53,64; 61,9</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66,07; 74,04</t>
+          <t>66,28; 74,07</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51,69; 60,29</t>
+          <t>51,0; 59,85</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53,96; 61,41</t>
+          <t>53,67; 61,22</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41,33; 49,81</t>
+          <t>41,51; 49,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>53,49; 61,69</t>
+          <t>53,08; 61,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40,48; 49,12</t>
+          <t>39,75; 48,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28,88; 37,71</t>
+          <t>29,12; 37,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>58,05; 65,43</t>
+          <t>57,57; 65,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,78; 72,53</t>
+          <t>65,11; 72,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,87; 60,67</t>
+          <t>52,76; 60,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,86; 74,75</t>
+          <t>37,71; 76,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>50,8; 56,85</t>
+          <t>50,73; 56,47</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60,84; 66,24</t>
+          <t>60,85; 65,89</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47,9; 53,83</t>
+          <t>48,0; 53,58</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,54; 66,65</t>
+          <t>35,08; 64,37</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>47,77; 55,26</t>
+          <t>47,2; 54,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>43,69; 51,63</t>
+          <t>43,83; 51,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47,97; 54,9</t>
+          <t>47,59; 55,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,98; 34,63</t>
+          <t>10,75; 34,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>59,95; 66,87</t>
+          <t>60,13; 66,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,17; 62,17</t>
+          <t>54,95; 62,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,79; 64,56</t>
+          <t>57,71; 64,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>41,78; 48,36</t>
+          <t>42,0; 48,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>54,95; 60,08</t>
+          <t>54,95; 60,09</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50,87; 56,01</t>
+          <t>50,71; 55,74</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54,07; 58,91</t>
+          <t>53,68; 58,8</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,66; 40,22</t>
+          <t>20,31; 40,17</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46,39; 50,01</t>
+          <t>46,41; 49,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>53,97; 57,43</t>
+          <t>53,99; 57,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50,46; 54,0</t>
+          <t>50,52; 53,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30,22; 41,85</t>
+          <t>29,55; 41,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>62,17; 65,77</t>
+          <t>62,3; 65,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>67,55; 70,8</t>
+          <t>67,7; 70,8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>62,12; 65,31</t>
+          <t>62,21; 65,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>44,17; 58,07</t>
+          <t>44,01; 58,13</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>54,87; 57,41</t>
+          <t>54,92; 57,42</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>61,35; 63,74</t>
+          <t>61,46; 63,82</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56,91; 59,33</t>
+          <t>57,0; 59,29</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>39,27; 48,31</t>
+          <t>39,36; 47,74</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación</t>
+          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>100887; 133644</t>
+          <t>101479; 133785</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>161880; 196639</t>
+          <t>164102; 195984</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>148806; 184454</t>
+          <t>148705; 184369</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>182235; 220788</t>
+          <t>180550; 220379</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>119788; 152581</t>
+          <t>118485; 152272</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>210924; 239520</t>
+          <t>210715; 238946</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>182796; 213246</t>
+          <t>183685; 213695</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>191234; 216126</t>
+          <t>191661; 217451</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>228735; 277200</t>
+          <t>230194; 276846</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>380820; 426898</t>
+          <t>381862; 429275</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>343331; 391090</t>
+          <t>337292; 386717</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>382105; 430001</t>
+          <t>381129; 427761</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>208036; 251658</t>
+          <t>209552; 253088</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>243428; 292439</t>
+          <t>243857; 289676</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>265080; 311997</t>
+          <t>264295; 311548</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>182810; 239029</t>
+          <t>181127; 237614</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>308974; 350884</t>
+          <t>309630; 350739</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>344534; 388920</t>
+          <t>346788; 387995</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>349832; 392340</t>
+          <t>350906; 392061</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>216796; 256500</t>
+          <t>214135; 254135</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>531532; 591631</t>
+          <t>530208; 591571</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>601793; 670152</t>
+          <t>598029; 662873</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>630108; 691916</t>
+          <t>627160; 690239</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>407324; 477595</t>
+          <t>409034; 481956</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>124645; 160024</t>
+          <t>125899; 161273</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>171872; 208827</t>
+          <t>175546; 210782</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>151825; 184234</t>
+          <t>151698; 185695</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>135963; 171711</t>
+          <t>137552; 171832</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>210147; 245189</t>
+          <t>211727; 246608</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>214126; 250052</t>
+          <t>215879; 251722</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>187049; 223280</t>
+          <t>190638; 225084</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>162748; 195022</t>
+          <t>162508; 194375</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>344685; 395700</t>
+          <t>343826; 395723</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>401395; 452247</t>
+          <t>400464; 450289</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>351341; 400950</t>
+          <t>351070; 399632</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>309735; 356503</t>
+          <t>305939; 355663</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>167195; 206839</t>
+          <t>167417; 203479</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>199818; 239794</t>
+          <t>201353; 241055</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>198023; 234397</t>
+          <t>196620; 234223</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>119321; 162324</t>
+          <t>117485; 160152</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>240960; 277355</t>
+          <t>240194; 275013</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>259504; 294440</t>
+          <t>257960; 296817</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>257448; 293493</t>
+          <t>255688; 292248</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>115696; 243908</t>
+          <t>117476; 245674</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>419244; 470708</t>
+          <t>417989; 470556</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>469575; 523689</t>
+          <t>470839; 523798</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>463002; 516493</t>
+          <t>464537; 519974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>243085; 386320</t>
+          <t>242747; 385896</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>86767; 114843</t>
+          <t>87056; 115767</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>105286; 134787</t>
+          <t>103894; 135658</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96460; 126195</t>
+          <t>95408; 124672</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17011; 31179</t>
+          <t>16809; 31164</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>121819; 149655</t>
+          <t>122109; 151397</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>169240; 190859</t>
+          <t>168200; 191825</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>126510; 154204</t>
+          <t>125845; 153846</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20405; 50076</t>
+          <t>21037; 50422</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>216155; 257031</t>
+          <t>216437; 256876</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>282244; 319435</t>
+          <t>280342; 318746</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>231795; 271705</t>
+          <t>234173; 274544</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>41729; 75380</t>
+          <t>41809; 75012</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>121104; 153717</t>
+          <t>121513; 154950</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>154564; 188653</t>
+          <t>153701; 186613</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>114309; 147689</t>
+          <t>113873; 146845</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>138780; 169115</t>
+          <t>140006; 171464</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>162153; 194944</t>
+          <t>163005; 195735</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>202212; 230049</t>
+          <t>202680; 230178</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>152067; 184219</t>
+          <t>154797; 186511</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>134668; 159944</t>
+          <t>135447; 160308</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>295246; 341664</t>
+          <t>294468; 339795</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>366035; 410185</t>
+          <t>367176; 410371</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>277205; 323288</t>
+          <t>273462; 320931</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>284223; 323465</t>
+          <t>282652; 322465</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>254160; 306352</t>
+          <t>255317; 303556</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>354532; 408884</t>
+          <t>351832; 408110</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>265799; 322522</t>
+          <t>260988; 317096</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>180304; 235440</t>
+          <t>181787; 231291</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>370468; 417567</t>
+          <t>367425; 415884</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>449463; 503226</t>
+          <t>451801; 501220</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>365494; 419435</t>
+          <t>364706; 417684</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>321544; 634828</t>
+          <t>320285; 652332</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>636636; 712527</t>
+          <t>635718; 707658</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>825445; 898623</t>
+          <t>825504; 893853</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>645652; 725579</t>
+          <t>646903; 722171</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>523696; 982054</t>
+          <t>516974; 948564</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>355303; 411049</t>
+          <t>351035; 407446</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>340412; 402278</t>
+          <t>341493; 399427</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>373470; 427455</t>
+          <t>370497; 428739</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>101941; 321602</t>
+          <t>99846; 322235</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>469728; 523918</t>
+          <t>471141; 522999</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>454511; 512169</t>
+          <t>452708; 511626</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>477427; 533370</t>
+          <t>476762; 533806</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>299841; 347069</t>
+          <t>301418; 345404</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>839196; 917622</t>
+          <t>839313; 917815</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>815487; 897776</t>
+          <t>812859; 893518</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>867657; 945322</t>
+          <t>861401; 943641</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>340114; 662278</t>
+          <t>334433; 661441</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1519872; 1638673</t>
+          <t>1520616; 1636835</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1849476; 1968067</t>
+          <t>1850019; 1965044</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1712701; 1832928</t>
+          <t>1714718; 1829476</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1045718; 1448031</t>
+          <t>1022275; 1443659</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2100896; 2222608</t>
+          <t>2105314; 2214989</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2403543; 2519341</t>
+          <t>2409124; 2519358</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2202021; 2314803</t>
+          <t>2204921; 2318325</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1639887; 2155738</t>
+          <t>1633608; 2158123</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3652324; 3821214</t>
+          <t>3655098; 3821684</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4285196; 4452118</t>
+          <t>4292739; 4457638</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3949120; 4116959</t>
+          <t>3954961; 4114052</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2816485; 3464703</t>
+          <t>2822782; 3424282</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,17; 49,0</t>
+          <t>37,34; 49,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55,68; 66,49</t>
+          <t>55,26; 66,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50,62; 62,76</t>
+          <t>49,74; 62,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57,97; 70,76</t>
+          <t>54,43; 65,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,42; 58,38</t>
+          <t>45,91; 58,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,36; 83,19</t>
+          <t>73,55; 83,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,62; 74,02</t>
+          <t>63,6; 74,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>66,17; 75,08</t>
+          <t>62,01; 71,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>43,12; 51,86</t>
+          <t>42,95; 51,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65,61; 73,76</t>
+          <t>65,71; 73,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57,91; 66,39</t>
+          <t>58,82; 66,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,41; 71,17</t>
+          <t>59,64; 66,93</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,46%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,5; 51,33</t>
+          <t>42,41; 51,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,24; 57,3</t>
+          <t>48,16; 57,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52,59; 61,99</t>
+          <t>53,23; 61,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,94; 45,84</t>
+          <t>34,69; 45,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>61,44; 69,6</t>
+          <t>61,32; 69,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,21; 74,08</t>
+          <t>66,02; 74,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,08; 74,95</t>
+          <t>66,84; 74,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>41,58; 49,35</t>
+          <t>41,12; 48,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53,18; 59,33</t>
+          <t>53,23; 59,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58,1; 64,4</t>
+          <t>58,43; 64,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61,15; 67,3</t>
+          <t>61,49; 67,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,58; 46,64</t>
+          <t>39,36; 45,79</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,63%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,49; 50,58</t>
+          <t>38,51; 50,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54,17; 65,05</t>
+          <t>54,31; 65,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47,62; 58,29</t>
+          <t>47,74; 58,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43,52; 54,37</t>
+          <t>42,66; 53,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63,12; 73,52</t>
+          <t>62,75; 73,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,3; 73,81</t>
+          <t>62,71; 73,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,69; 66,93</t>
+          <t>56,75; 67,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,55; 55,67</t>
+          <t>46,37; 55,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52,55; 60,48</t>
+          <t>52,66; 60,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>60,21; 67,71</t>
+          <t>60,47; 67,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>53,61; 61,02</t>
+          <t>53,33; 61,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>45,99; 53,47</t>
+          <t>46,42; 53,17</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>48,11%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,68; 56,73</t>
+          <t>46,94; 57,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,84; 64,46</t>
+          <t>53,78; 64,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53,15; 63,31</t>
+          <t>53,21; 63,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37,59; 51,24</t>
+          <t>37,57; 50,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>64,66; 74,04</t>
+          <t>64,89; 74,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,32; 76,31</t>
+          <t>66,15; 75,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,02; 75,46</t>
+          <t>66,27; 75,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,69; 51,64</t>
+          <t>46,31; 56,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>57,25; 64,45</t>
+          <t>57,32; 64,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61,71; 68,66</t>
+          <t>61,72; 68,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61,35; 68,67</t>
+          <t>61,23; 68,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,79; 48,95</t>
+          <t>43,88; 52,16</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,82; 56,94</t>
+          <t>43,36; 57,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48,86; 63,8</t>
+          <t>49,24; 63,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,17; 59,02</t>
+          <t>46,04; 59,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,4; 17,44</t>
+          <t>9,07; 16,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,8; 72,9</t>
+          <t>59,16; 72,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>76,6; 87,36</t>
+          <t>76,67; 86,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,57; 70,38</t>
+          <t>58,32; 71,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,13; 19,48</t>
+          <t>14,74; 21,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>52,66; 62,5</t>
+          <t>52,78; 62,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64,86; 73,75</t>
+          <t>64,67; 73,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54,48; 63,88</t>
+          <t>53,55; 62,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,56; 17,14</t>
+          <t>12,96; 18,17</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,1%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44,87; 57,22</t>
+          <t>45,03; 56,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>56,1; 68,11</t>
+          <t>57,07; 69,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43,28; 55,81</t>
+          <t>43,44; 55,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51,92; 63,59</t>
+          <t>52,29; 62,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58,6; 70,37</t>
+          <t>58,4; 69,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72,38; 82,2</t>
+          <t>71,99; 82,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>56,68; 68,29</t>
+          <t>54,98; 67,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>52,69; 62,36</t>
+          <t>51,93; 61,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53,64; 61,9</t>
+          <t>53,61; 62,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66,28; 74,07</t>
+          <t>65,55; 73,83</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51,0; 59,85</t>
+          <t>51,6; 60,09</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53,67; 61,22</t>
+          <t>53,28; 60,79</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>36,7%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41,51; 49,36</t>
+          <t>41,11; 49,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>53,08; 61,57</t>
+          <t>53,68; 61,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39,75; 48,3</t>
+          <t>40,8; 48,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29,12; 37,05</t>
+          <t>29,37; 37,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>57,57; 65,16</t>
+          <t>57,4; 65,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,11; 72,24</t>
+          <t>65,4; 72,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,76; 60,42</t>
+          <t>52,46; 60,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,71; 76,81</t>
+          <t>37,12; 43,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>50,73; 56,47</t>
+          <t>50,72; 56,54</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60,85; 65,89</t>
+          <t>60,6; 65,73</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48,0; 53,58</t>
+          <t>47,91; 53,32</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,08; 64,37</t>
+          <t>34,2; 39,34</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>38,77%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>47,2; 54,78</t>
+          <t>47,48; 55,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>43,83; 51,27</t>
+          <t>43,74; 51,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47,59; 55,07</t>
+          <t>47,35; 54,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,75; 34,7</t>
+          <t>29,5; 36,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>60,13; 66,75</t>
+          <t>59,46; 66,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>54,95; 62,1</t>
+          <t>55,38; 62,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,71; 64,61</t>
+          <t>57,36; 64,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>42,0; 48,12</t>
+          <t>41,8; 48,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>54,95; 60,09</t>
+          <t>54,8; 59,91</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50,71; 55,74</t>
+          <t>50,68; 55,54</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53,68; 58,8</t>
+          <t>53,88; 58,66</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,31; 40,17</t>
+          <t>36,57; 41,17</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,01%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46,41; 49,96</t>
+          <t>46,5; 50,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>53,99; 57,34</t>
+          <t>53,81; 57,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50,52; 53,9</t>
+          <t>50,34; 53,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29,55; 41,73</t>
+          <t>37,91; 41,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>62,3; 65,55</t>
+          <t>62,11; 65,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>67,7; 70,8</t>
+          <t>67,48; 70,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>62,21; 65,41</t>
+          <t>62,08; 65,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>44,01; 58,13</t>
+          <t>44,93; 47,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>54,92; 57,42</t>
+          <t>54,84; 57,32</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>61,46; 63,82</t>
+          <t>61,34; 63,73</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>57,0; 59,29</t>
+          <t>56,89; 59,25</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>39,36; 47,74</t>
+          <t>41,85; 44,24</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>201413</t>
+          <t>191271</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>204585</t>
+          <t>211079</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>405997</t>
+          <t>402350</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>101479; 133785</t>
+          <t>101934; 134651</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>164102; 195984</t>
+          <t>162868; 196500</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>148705; 184369</t>
+          <t>146113; 182602</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>180550; 220379</t>
+          <t>173542; 208958</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>118485; 152272</t>
+          <t>119762; 152517</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>210715; 238946</t>
+          <t>211275; 239190</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>183685; 213695</t>
+          <t>183629; 215660</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>191661; 217451</t>
+          <t>196002; 224824</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>230194; 276846</t>
+          <t>229313; 276193</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>381862; 429275</t>
+          <t>382440; 427313</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>337292; 386717</t>
+          <t>342626; 388795</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>381129; 427761</t>
+          <t>378638; 424939</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>209116</t>
+          <t>210802</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>234843</t>
+          <t>246507</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>443959</t>
+          <t>457309</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>209552; 253088</t>
+          <t>209103; 254418</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>243857; 289676</t>
+          <t>243478; 289442</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>264295; 311548</t>
+          <t>267537; 311300</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>181127; 237614</t>
+          <t>184082; 239555</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>309630; 350739</t>
+          <t>309018; 351222</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>346788; 387995</t>
+          <t>345785; 389166</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>350906; 392061</t>
+          <t>349622; 390777</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>214135; 254135</t>
+          <t>224701; 267221</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>530208; 591571</t>
+          <t>530743; 592652</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>598029; 662873</t>
+          <t>601447; 667159</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>627160; 690239</t>
+          <t>630638; 694251</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>409034; 481956</t>
+          <t>423964; 493253</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>154192</t>
+          <t>152561</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>178378</t>
+          <t>181114</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>332569</t>
+          <t>333676</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>125899; 161273</t>
+          <t>122777; 160557</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>175546; 210782</t>
+          <t>175994; 211687</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>151698; 185695</t>
+          <t>152074; 186496</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>137552; 171832</t>
+          <t>134814; 169500</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>211727; 246608</t>
+          <t>210473; 245076</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>215879; 251722</t>
+          <t>213868; 250615</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>190638; 225084</t>
+          <t>190870; 226632</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>162508; 194375</t>
+          <t>165236; 197030</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>343826; 395723</t>
+          <t>344552; 395968</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>400464; 450289</t>
+          <t>402179; 451761</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>351070; 399632</t>
+          <t>349253; 399653</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>305939; 355663</t>
+          <t>312129; 357474</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>139789</t>
+          <t>165896</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>193728</t>
+          <t>216663</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>333516</t>
+          <t>382560</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>167417; 203479</t>
+          <t>168367; 204835</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>201353; 241055</t>
+          <t>201125; 239855</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>196620; 234223</t>
+          <t>196851; 235501</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>117485; 160152</t>
+          <t>140188; 189625</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>240194; 275013</t>
+          <t>241034; 275601</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>257960; 296817</t>
+          <t>257283; 293806</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>255688; 292248</t>
+          <t>256656; 293489</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>117476; 245674</t>
+          <t>195407; 236956</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>417989; 470556</t>
+          <t>418486; 472507</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>470839; 523798</t>
+          <t>470897; 524259</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>464537; 519974</t>
+          <t>463645; 518245</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>242747; 385896</t>
+          <t>348883; 414717</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23279</t>
+          <t>25319</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38655</t>
+          <t>41267</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61934</t>
+          <t>66586</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>87056; 115767</t>
+          <t>88158; 116744</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>103894; 135658</t>
+          <t>104701; 134213</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>95408; 124672</t>
+          <t>97243; 126601</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16809; 31164</t>
+          <t>18661; 33750</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>122109; 151397</t>
+          <t>122847; 149657</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>168200; 191825</t>
+          <t>168371; 190606</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>125845; 153846</t>
+          <t>127477; 155431</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21037; 50422</t>
+          <t>33752; 49457</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>216437; 256876</t>
+          <t>216904; 257918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>280342; 318746</t>
+          <t>279490; 319544</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>234173; 274544</t>
+          <t>230178; 270087</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>41809; 75012</t>
+          <t>56333; 78947</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>155020</t>
+          <t>155289</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>147720</t>
+          <t>149875</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>302741</t>
+          <t>305164</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>121513; 154950</t>
+          <t>121949; 153344</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>153701; 186613</t>
+          <t>156361; 190032</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>113873; 146845</t>
+          <t>114304; 146777</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>140006; 171464</t>
+          <t>141560; 169433</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>163005; 195735</t>
+          <t>162428; 194003</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>202680; 230178</t>
+          <t>201594; 230203</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>154797; 186511</t>
+          <t>150146; 183578</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>135447; 160308</t>
+          <t>136973; 162621</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>294468; 339795</t>
+          <t>294312; 340643</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>367176; 410371</t>
+          <t>363164; 409026</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>273462; 320931</t>
+          <t>276675; 322202</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>282652; 322465</t>
+          <t>284760; 324900</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>206602</t>
+          <t>236790</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>456895</t>
+          <t>310667</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>663497</t>
+          <t>547457</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>255317; 303556</t>
+          <t>252847; 305044</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>351832; 408110</t>
+          <t>355764; 409978</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>260988; 317096</t>
+          <t>267880; 318903</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>181787; 231291</t>
+          <t>211378; 266316</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>367425; 415884</t>
+          <t>366353; 415770</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>451801; 501220</t>
+          <t>453780; 503582</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>364706; 417684</t>
+          <t>362685; 417160</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>320285; 652332</t>
+          <t>286607; 338455</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>635718; 707658</t>
+          <t>635697; 708604</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>825504; 893853</t>
+          <t>822096; 891768</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>646903; 722171</t>
+          <t>645696; 718717</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>516974; 948564</t>
+          <t>510205; 586910</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>229364</t>
+          <t>260054</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>324014</t>
+          <t>371616</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>553378</t>
+          <t>631670</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>351035; 407446</t>
+          <t>353118; 410541</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>341493; 399427</t>
+          <t>340795; 398923</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>370497; 428739</t>
+          <t>368645; 427949</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>99846; 322235</t>
+          <t>235464; 289115</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>471141; 522999</t>
+          <t>465868; 523013</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>452708; 511626</t>
+          <t>456240; 512507</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>476762; 533806</t>
+          <t>473911; 533505</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>301418; 345404</t>
+          <t>347521; 399324</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>839313; 917815</t>
+          <t>836993; 914949</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>812859; 893518</t>
+          <t>812333; 890324</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>861401; 943641</t>
+          <t>864671; 941364</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>334433; 661441</t>
+          <t>595880; 670879</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1318774</t>
+          <t>1397982</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1778817</t>
+          <t>1728788</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3097592</t>
+          <t>3126771</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1520616; 1636835</t>
+          <t>1523547; 1639290</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1850019; 1965044</t>
+          <t>1844031; 1970458</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1714718; 1829476</t>
+          <t>1708608; 1830690</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1022275; 1443659</t>
+          <t>1339425; 1464117</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2105314; 2214989</t>
+          <t>2098769; 2211245</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2409124; 2519358</t>
+          <t>2401120; 2517117</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2204921; 2318325</t>
+          <t>2200429; 2313834</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1633608; 2158123</t>
+          <t>1679038; 1785648</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3655098; 3821684</t>
+          <t>3649928; 3815091</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4292739; 4457638</t>
+          <t>4284597; 4451431</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3954961; 4114052</t>
+          <t>3947609; 4111313</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2822782; 3424282</t>
+          <t>3042214; 3215997</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna condición, enfermedad crónica o limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
